--- a/output/北塩原村_レビュー対応_第3回.xlsx
+++ b/output/北塩原村_レビュー対応_第3回.xlsx
@@ -1390,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1736,89 +1736,95 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Ⅲ</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>令和6年・令和7年の数値を受領した後（令和8年10月13日）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>療育と精神は令和3年から令和8年までの6点で回帰し、身体は令和6年・令和7年が判明していないため所持率法（基準年 令和8年）で置く</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>策定委員会資料から令和6年・令和7年の療育・精神の所持者数を受領したことにより、仮説Ⅰ〜Ⅱ-bの幅が収束する。令和6年・令和7年が村の手帳台帳による実数であることが前提であり、Ｍ-124で出所を確かめる。身体の令和6年・令和7年が得られれば3手帳すべてを回帰で組める</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>3. 試算（手帳別に別の係数を用いる）</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>仮説</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>令和9年</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>令和10年</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>令和11年</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>身体障害者手帳</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>療育手帳</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="15" t="n">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
     </row>
@@ -1826,83 +1832,83 @@
       <c r="A25" s="5" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>精神障害者保健福祉手帳</t>
+          <t>療育手帳</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr"/>
       <c r="D25" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E26" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F26" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="G25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="8" t="inlineStr"/>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
-      <c r="D26" s="18" t="n">
+      <c r="C27" s="9" t="inlineStr"/>
+      <c r="D27" s="18" t="n">
         <v>152</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E27" s="18" t="n">
         <v>151</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F27" s="18" t="n">
         <v>149</v>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>実績だけで組める唯一の方法。ただし令和6〜8年の実績が無いため、3年分の空白をまたいで延ばしている</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Ⅰ-b</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>身体障害者手帳</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>103</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>療育手帳</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr"/>
       <c r="D28" s="15" t="n">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
     </row>
@@ -1910,83 +1916,83 @@
       <c r="A29" s="5" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>精神障害者保健福祉手帳</t>
+          <t>療育手帳</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr"/>
       <c r="D29" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E30" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F30" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="G29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="8" t="inlineStr"/>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="18" t="n">
+      <c r="C31" s="9" t="inlineStr"/>
+      <c r="D31" s="18" t="n">
         <v>145</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E31" s="18" t="n">
         <v>141</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F31" s="18" t="n">
         <v>139</v>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>人口減少の影響を反映する。所持率そのものの変化は捉えない。精神のように所持率が動いている区分では向きを誤る</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>身体障害者手帳</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="15" t="n">
-        <v>124</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>119</v>
-      </c>
-      <c r="G31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>療育手帳</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr"/>
       <c r="D32" s="15" t="n">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="G32" s="6" t="inlineStr"/>
     </row>
@@ -1994,83 +2000,83 @@
       <c r="A33" s="5" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>精神障害者保健福祉手帳</t>
+          <t>療育手帳</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr"/>
       <c r="D33" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E34" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="F33" s="15" t="n">
+      <c r="F34" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="G33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="8" t="inlineStr"/>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr"/>
-      <c r="D34" s="18" t="n">
+      <c r="C35" s="9" t="inlineStr"/>
+      <c r="D35" s="18" t="n">
         <v>177</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E35" s="18" t="n">
         <v>173</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F35" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>基礎とする令和8年の値が他メンバー版のワークシートの推計（仮置き）であり、実数ではない。実数が判明するまで確定できない</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Ⅱ-b</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>身体障害者手帳</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="15" t="n">
-        <v>131</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>136</v>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>療育手帳</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="15" t="n">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
     </row>
@@ -2078,106 +2084,217 @@
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>精神障害者保健福祉手帳</t>
+          <t>療育手帳</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr"/>
       <c r="D37" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E38" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F38" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="G37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="8" t="inlineStr"/>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="8" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr"/>
-      <c r="D38" s="18" t="n">
+      <c r="C39" s="9" t="inlineStr"/>
+      <c r="D39" s="18" t="n">
         <v>189</v>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E39" s="18" t="n">
         <v>198</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F39" s="18" t="n">
         <v>206</v>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>人口が減り続ける中で所持者だけが年8人増え続ける想定になる。幅の上限を示すためのものであり、採らない</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Ⅲ</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="15" t="n">
+        <v>124</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>療育手帳</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="8" t="inlineStr"/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr"/>
+      <c r="D43" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>181</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>181</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>策定委員会資料から令和6年・令和7年の療育・精神の所持者数を受領したことにより、仮説Ⅰ〜Ⅱ-bの幅が収束する。令和6年・令和7年が村の手帳台帳による実数であることが前提であり、Ｍ-124で出所を確かめる。身体の令和6年・令和7年が得られれば3手帳すべてを回帰で組める</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>4. 読み取り</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>令和11年の合計は139人から206人まで67人の幅がある。令和8年の仮置きの181人に対して3分の1を超える幅であり、この幅のまま計画に単一の数値を置くことはできない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>幅の大半は、令和5年から令和8年までの25人の増加を実際の増加と見るか、数え方の違いと見るかで生じている。令和6年・令和7年の実数が1件入れば、どちらであるかが決まる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>手帳別では向きが分かれている。平成31年〜令和5年の回帰の傾きは、身体が－2.30人/年、療育が－0.30人/年、精神が＋1.00人/年である。三つの手帳を同じ伸び率で動かすことはしない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>仮説Ⅱ-bは幅の上限を示すためのものであり、採らない。人口が年50人ずつ減る中で所持者だけが年8人増え続ける想定になる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>人口そのものにも未決の点がある。本シートは正本 表２-１（令和11年2,166人）に合わせているが、村のこども・子育て計画のコーホート変化率法による公式推計は令和11年2,185人・老年人口1,051人（高齢化率48.1％）であり、老年人口の向きが逆である。どちらを用いるかは既に起票済み（網羅性点検 第2章1）。人口が定まらないと所持率法の推計も定まらない。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>令和11年の合計は139人から206人まで67人の幅がある。令和8年の仮置きの181人に対して3分の1を超える幅であり、この幅のまま計画に単一の数値を置くことはできない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>幅の大半は、令和5年から令和8年までの25人の増加を実際の増加と見るか、数え方の違いと見るかで生じている。令和6年・令和7年の実数が1件入れば、どちらであるかが決まる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>手帳別では向きが分かれている。平成31年〜令和5年の回帰の傾きは、身体が－2.30人/年、療育が－0.30人/年、精神が＋1.00人/年である。三つの手帳を同じ伸び率で動かすことはしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>仮説Ⅱ-bは幅の上限を示すためのものであり、採らない。人口が年50人ずつ減る中で所持者だけが年8人増え続ける想定になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>人口そのものにも未決の点がある。本シートは正本 表２-１（令和11年2,166人）に合わせているが、村のこども・子育て計画のコーホート変化率法による公式推計は令和11年2,185人・老年人口1,051人（高齢化率48.1％）であり、老年人口の向きが逆である。どちらを用いるかは既に起票済み（網羅性点検 第2章1）。人口が定まらないと所持率法の推計も定まらない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>【令和8年10月13日 追記】策定委員会資料から令和6年・令和7年の療育・精神の所持者数を受領した（療育13人・15人、精神33人・36人）。これにより仮説Ⅲのとおり令和11年の合計は181人へ収束する。令和6年・令和7年が村の手帳台帳による実数であることが前提であり、Ｍ-124で出所を確かめる。身体の令和6年・令和7年が得られれば3手帳すべてを回帰で組める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>年齢階級別の所持者数が得られれば、年齢階級別の所持率による推計に切り替える。高齢化率が上がる一方で老年人口が減る本村では、全体の所持率を一定とする方法より精度が高い（Ｍ-113の④）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A46:G46"/>
   </mergeCells>
